--- a/resources/table/board.xlsx
+++ b/resources/table/board.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\CSHYEON\Data\git\game\c++\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108A7C74-D341-4F0A-ADE9-5806AAF2C09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEC21CB-4B49-4491-970B-20F6F2997ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{182A1246-FECB-4C40-8695-2AB823971D67}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{182A1246-FECB-4C40-8695-2AB823971D67}"/>
   </bookViews>
   <sheets>
     <sheet name="board" sheetId="1" r:id="rId1"/>
@@ -74,11 +74,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>admin(true)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>level(10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>role(ADMIN)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -521,7 +521,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -532,7 +532,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
